--- a/AI_Audit_Log/Dinh Do Gia Huy AI_Log.xlsx
+++ b/AI_Audit_Log/Dinh Do Gia Huy AI_Log.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d2gia\OneDrive\ドキュメント\Kỳ 3\LAB211\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d2gia\OneDrive\ドキュメント\LAB1\Group1-LAB211\AI_Audit_Log\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E826C84D-8F10-4D22-B1CB-568D7EFFE4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD8BB9E5-2FBB-47A4-B751-35EF737B140B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="172">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -447,9 +447,6 @@
     <t>Employee Payroll Management Simulation</t>
   </si>
   <si>
-    <t>Does the salary calculation formula for FULLTIME and PARTTIME employees in DataGenerator fully comply with the LAB211 project specification?</t>
-  </si>
-  <si>
     <t>Critical Thinking: AI đúng về cấu trúc công thức nhưng các tỷ lệ Bonus/Tax chỉ là giả định.
 Contextualization: Đề không quy định chi tiết chính sách lương.
 Creative Synthesis: Đối chiếu rubric và ghi rõ các giả định (OT 1.5×, Bonus 5%, Tax 10%/5%).
@@ -474,9 +471,6 @@
     <t>Verification</t>
   </si>
   <si>
-    <t>How are FULLTIME and PARTTIME employee salaries calculated, and what salary ranges are generated in DataGenerator?</t>
-  </si>
-  <si>
     <t>Thắc mắc cách tính lương của nhân viên FULLTIME và PARTTIME và mức lương được sinh nằm trong khoảng nào.</t>
   </si>
   <si>
@@ -489,9 +483,6 @@
 Decision Ownership:Giữ nguyên khoảng lương hiện tại vì phù hợp cho Payroll Simulation và testing.</t>
   </si>
   <si>
-    <t>Why is Random initialized with a fixed seed value of 42?</t>
-  </si>
-  <si>
     <t>Critical Thinking: Cùng seed sẽ tạo cùng dữ liệu mỗi lần chạy.
 Contextualization: Dễ debug và so sánh kết quả simulation.
 Creative Synthesis: Giữ seed cố định trong DataGenerator.
@@ -517,9 +508,6 @@
   </si>
   <si>
     <t>Problem-Solving</t>
-  </si>
-  <si>
-    <t>How can I format salary output in Java to avoid scientific notation and round values to the nearest thousand?</t>
   </si>
   <si>
     <t>Kết quả lương trong Java đang hiển thị dạng scientific notation (1.3622727E7), khó đọc và chưa làm tròn số tiền.</t>
@@ -611,6 +599,18 @@
   </si>
   <si>
     <t>Gemini</t>
+  </si>
+  <si>
+    <t>cách tính lương của nhân viên parttime và fulltime có thực sự giống như yêu cầu của project k</t>
+  </si>
+  <si>
+    <t>tôi muốn hỏi là lương của nhân viên parttime và fulltime được tính bằng cách nào và lương nằm trong khoảng nào</t>
+  </si>
+  <si>
+    <t>Tại sao biến Random được khởi tạo với seed(42) fixed</t>
+  </si>
+  <si>
+    <t>làm tròn số lương và sửa lại format</t>
   </si>
 </sst>
 </file>
@@ -763,7 +763,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -800,6 +800,27 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -815,22 +836,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1145,14 +1150,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
     </row>
     <row r="3" spans="1:6" ht="17.399999999999999">
       <c r="A3" s="1" t="s">
@@ -1256,7 +1261,7 @@
         <v>20</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>23</v>
@@ -1268,7 +1273,7 @@
         <v>22</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>21</v>
@@ -1277,7 +1282,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="7" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -1375,40 +1380,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:8" ht="40.049999999999997" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="18" t="s">
         <v>39</v>
       </c>
       <c r="E3" s="6" t="s">
@@ -1420,7 +1425,7 @@
       <c r="G3" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="24" t="s">
+      <c r="H3" s="18" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1504,97 +1509,96 @@
     </row>
     <row r="7" spans="1:8" ht="100.2" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E7" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="H7" s="27"/>
     </row>
     <row r="8" spans="1:8" ht="117.6" customHeight="1">
       <c r="A8" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="B8" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="C8" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="C8" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="D8" s="7" t="s">
+      <c r="E8" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>143</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>144</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>145</v>
       </c>
       <c r="H8" s="7"/>
     </row>
     <row r="9" spans="1:8" ht="79.95" customHeight="1">
       <c r="A9" s="7" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>151</v>
-      </c>
       <c r="D9" s="7" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E9" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>149</v>
-      </c>
       <c r="G9" s="7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H9" s="7"/>
     </row>
     <row r="10" spans="1:8" ht="143.4" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="B10" s="25" t="s">
-        <v>154</v>
+        <v>150</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>151</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>33</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="F10" s="26" t="s">
-        <v>157</v>
+        <v>171</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>153</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H10" s="7"/>
     </row>
@@ -1779,24 +1783,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
     </row>
     <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1">
       <c r="A3" s="6" t="s">
@@ -1849,43 +1853,43 @@
       <c r="F5" s="7"/>
     </row>
     <row r="6" spans="1:6" ht="60" customHeight="1">
-      <c r="A6" s="29">
-        <v>2</v>
-      </c>
-      <c r="B6" s="28" t="s">
+      <c r="A6" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C6" s="7" t="s">
+    </row>
+    <row r="7" spans="1:6" ht="60" customHeight="1">
+      <c r="A7" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="B7" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="C7" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="E7" s="22" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="60" customHeight="1">
-      <c r="A7" s="7">
-        <v>3</v>
-      </c>
-      <c r="B7" s="28" t="s">
+      <c r="F7" s="7" t="s">
         <v>164</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="E7" s="29" t="s">
-        <v>167</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="60" customHeight="1">
@@ -2116,20 +2120,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
     </row>
     <row r="4" spans="1:4" ht="17.399999999999999">
       <c r="A4" s="1" t="s">

--- a/AI_Audit_Log/Dinh Do Gia Huy AI_Log.xlsx
+++ b/AI_Audit_Log/Dinh Do Gia Huy AI_Log.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d2gia\OneDrive\ドキュメント\LAB1\Group1-LAB211\AI_Audit_Log\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LAB211\Group1-LAB211\AI_Audit_Log\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD8BB9E5-2FBB-47A4-B751-35EF737B140B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D506403F-F76D-4AFD-927B-A4E68DD09D36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="222">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -174,75 +174,15 @@
     <t>DECISION</t>
   </si>
   <si>
-    <t>Cần chia nhỏ requirement</t>
-  </si>
-  <si>
-    <t>Break down student management into modules</t>
-  </si>
-  <si>
-    <t>AI suggested 10 modules: User, Student, Course, Grade, Attendance, Report, Export, Import, Settings, Dashboard</t>
-  </si>
-  <si>
-    <t>Critical Thinking: 10 modules quá nhiều cho project 300 LOC.
-Contextualization: Project scope nhỏ, chỉ cần core functions.
-Creative Synthesis: Tôi gộp thành 5 modules: Student, Grade, File I/O, Validation, UI.
-Decision: Chọn 5 modules vì đủ để implement requirements mà không phức tạp.</t>
-  </si>
-  <si>
-    <t>Screenshot comparison 10 vs 5</t>
-  </si>
-  <si>
     <t>002</t>
   </si>
   <si>
     <t>PROBLEM-SOLVING</t>
   </si>
   <si>
-    <t>Search by name quá chậm với 10K records</t>
-  </si>
-  <si>
-    <t>How to optimize search for player name in 10,000 records?</t>
-  </si>
-  <si>
-    <t>AI suggested Binary Search with O(log n) complexity</t>
-  </si>
-  <si>
-    <t>Critical Thinking: Binary Search cần sort trước → O(n log n). Với partial match không phù hợp.
-Contextualization: Requirements yêu cầu partial name search.
-Creative Synthesis: Test 3 approaches: Binary Search, Linear Search, HashMap. HashMap fastest (2ms).
-Decision: Chọn HashMap trade-off memory cho speed.</t>
-  </si>
-  <si>
-    <t>Code snippet + timing comparison</t>
-  </si>
-  <si>
     <t>003</t>
   </si>
   <si>
-    <t>VERIFICATION</t>
-  </si>
-  <si>
-    <t>Literature Review</t>
-  </si>
-  <si>
-    <t>Cần verify paper AI cite</t>
-  </si>
-  <si>
-    <t>Is the paper 'Smith et al. 2023 on IoT anomaly detection' a real publication?</t>
-  </si>
-  <si>
-    <t>AI confirmed it exists and provided summary</t>
-  </si>
-  <si>
-    <t>Critical Thinking: HALLUCINATION DETECTED! Search Google Scholar → paper NOT FOUND.
-Contextualization: AI fabricated paper to answer my question.
-Creative Synthesis: Found real paper 'Jones et al. 2022' with similar topic.
-Decision: Replace with verified paper from Google Scholar.</t>
-  </si>
-  <si>
-    <t>Google Scholar screenshot</t>
-  </si>
-  <si>
     <t>HALLUCINATION DETECTION LOG (BẮT BUỘC)</t>
   </si>
   <si>
@@ -268,18 +208,6 @@
   </si>
   <si>
     <t>Fabrication</t>
-  </si>
-  <si>
-    <t>Paper 'Smith et al. 2023' exists</t>
-  </si>
-  <si>
-    <t>Paper NOT FOUND on Google Scholar</t>
-  </si>
-  <si>
-    <t>Searched Google Scholar, ResearchGate</t>
-  </si>
-  <si>
-    <t>Used real paper 'Jones et al. 2022'</t>
   </si>
   <si>
     <t>HALLUCINATION TYPES REFERENCE:</t>
@@ -511,47 +439,6 @@
   </si>
   <si>
     <t>Kết quả lương trong Java đang hiển thị dạng scientific notation (1.3622727E7), khó đọc và chưa làm tròn số tiền.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The AI suggested using </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>DecimalFormat</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to display numbers with comma separators and using </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>Math.ceil(value / 1000.0) * 1000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to round salary values up to the nearest thousand.</t>
-    </r>
   </si>
   <si>
     <t>Critical Thinking: Tôi kiểm tra lại output và xác nhận Java tự động hiển thị kiểu double dưới dạng scientific notation khi số quá lớn.
@@ -611,6 +498,243 @@
   </si>
   <si>
     <t>làm tròn số lương và sửa lại format</t>
+  </si>
+  <si>
+    <t>#005</t>
+  </si>
+  <si>
+    <t>#006</t>
+  </si>
+  <si>
+    <t>#007</t>
+  </si>
+  <si>
+    <t>#008</t>
+  </si>
+  <si>
+    <t>#009</t>
+  </si>
+  <si>
+    <t>#010</t>
+  </si>
+  <si>
+    <t>Không biết vì sao update(), delete(), count() không tồn tại.</t>
+  </si>
+  <si>
+    <t>The method update(Employee) is undefined for EmployeeRepository.</t>
+  </si>
+  <si>
+    <t>AI giải thích EmployeeRepository chưa kế thừa CsvRepository hoặc CRUD chưa được thêm.</t>
+  </si>
+  <si>
+    <t>PROBLEM</t>
+  </si>
+  <si>
+    <t>Lỗi NullPointerException khi Create Employee.</t>
+  </si>
+  <si>
+    <t>Cannot invoke EmpType.name() because empType is null</t>
+  </si>
+  <si>
+    <t>AI xác định empType chưa được gán trước khi ghi CSV.</t>
+  </si>
+  <si>
+    <t>Design</t>
+  </si>
+  <si>
+    <t>Có nên dùng static trong SalaryCalculator.</t>
+  </si>
+  <si>
+    <t>Tôi muốn tạo object thay vì static.</t>
+  </si>
+  <si>
+    <t>AI giải thích sự khác nhau giữa static và object.</t>
+  </si>
+  <si>
+    <t>AI gợi ý sử dụng Java Reflection (`Field.setAccessible(true)`) để inject private static final FILE_PATH trong JUnit 5 test là approach tốt nhất.</t>
+  </si>
+  <si>
+    <t>Reflection approach có nhiều vấn đề: (1) Có thể fail với SecurityManager trong một số JVM config. (2) Brittle – nếu rename field sẽ break silently. (3) Không cần thiết vì đã có cách clean hơn với abstract method pattern.</t>
+  </si>
+  <si>
+    <t>Thử cả hai approach: reflection test vs anonymous subclass override. Reflection gây warning 'WARNING: An illegal reflective access operation has occurred' trên Java 11+. Anonymous subclass không có warning và compile-safe.</t>
+  </si>
+  <si>
+    <t>Dùng anonymous subclass override `getFilePath()` thay vì reflection: `new EmployeeRepository() { @Override protected String getFilePath() { return tempDir + "/test.csv"; } }`. Document thành 'Repository Test Pattern' cho team.</t>
+  </si>
+  <si>
+    <t>Pattern Recognition – Repository Test</t>
+  </si>
+  <si>
+    <t>JUnit 5 test với @TempDir không thể redirect EmployeeRepository về temp file vì FILE_PATH là private static final – không inject được.</t>
+  </si>
+  <si>
+    <t>Làm thế nào để test CsvRepository subclass với JUnit 5 @TempDir khi file path là private static final và không có setter/constructor injection?</t>
+  </si>
+  <si>
+    <t>AI gợi ý 3 approaches: (1) reflection để set field, (2) subclass override getFilePath(), (3) environment variable. Recommend dùng anonymous subclass override getFilePath().</t>
+  </si>
+  <si>
+    <t>Critical Thinking: AI đúng, anonymous subclass là cách clean nhất. Reflection approach brittle và có thể fail với SecurityManager.
+Contextualization: Team đã commit code với private static final FILE_PATH – không thể thay đổi Vy's code vì sẽ gây merge conflict. Cần workaround không đụng production code.
+Creative Synthesis: Tôi dùng anonymous subclass trong test: `new EmployeeRepository() { @Override protected String getFilePath() { return tempDir + "/employees.csv"; } }`. Clean và không cần thay production code.
+Decision Ownership: Document pattern này làm 'Repository Test Pattern' cho team biết dùng lại.</t>
+  </si>
+  <si>
+    <t>Algorithms – Optimistic Lock</t>
+  </si>
+  <si>
+    <t>Cần chọn cơ chế chống double payment cho PayrollEntry khi nhiều thread xử lý đồng thời – synchronized block hay optimistic lock với version field?</t>
+  </si>
+  <si>
+    <t>So sánh synchronized block vs optimistic locking (version field) để chống double payment trong PayrollEntryRepository. Trường hợp nào nên dùng cái nào?</t>
+  </si>
+  <si>
+    <t>AI giải thích: synchronized đơn giản nhưng throughput thấp (thread phải chờ). Optimistic lock throughput cao hơn nhưng cần retry logic khi version conflict.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: AI đúng về trade-off. Với project này (simulation, không phải production), cả hai đều valid. Nhưng version field đã có trong PayrollEntry.csv schema (cột 13).
+Contextualization: Week 7 yêu cầu implement và SO SÁNH 4 strategies – cần implement cả hai để compare, không chỉ chọn 1.
+Creative Synthesis: PayrollEntry.version field dùng cho optimistic lock. processWithSync() dùng synchronized keyword. processWithOptimistic() check version trước khi update. Cả hai trong cùng repository.
+Decision Ownership: Implement cả hai methods trong PayrollEntryRepository: processWithSync() và processWithOptimistic(). Test PayrollEntryRepositoryTest kiểm tra 3 thread đồng thời.</t>
+  </si>
+  <si>
+    <t>Decomposition – View Layer Design</t>
+  </si>
+  <si>
+    <t>Thiết kế View layer cho hệ thống: cần bao nhiêu View class và responsibility của mỗi class là gì?</t>
+  </si>
+  <si>
+    <t>Làm thế nào để thiết kế View layer cho Employee Payroll Management console app đúng MVC, View chỉ được display và collect input, không tính toán?</t>
+  </si>
+  <si>
+    <t>AI đề xuất 4 View class: MainView (menu chính), PayrollView (payroll operations), LeaveView (leave management), ReportView (báo cáo). Main.java là entry point.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: AI đúng về phân chia 4 View. Tuy nhiên AI không nhắc đến constraint: View KHÔNG ĐƯỢC gọi SalaryCalculator trực tiếp – mọi calculation đều qua Controller.
+Contextualization: Rubric của LAB211 penalize nếu View access Model trực tiếp để tính toán. View chỉ được gọi Controller methods.
+Creative Synthesis: Tôi thêm rule: View chỉ gọi controller.processPayroll(), controller.approveLeave() – không bao giờ new SalaryCalculator() trong View. Comment explicit trong code.
+Decision Ownership: MainView + PayrollView + LeaveView + ReportView + Main.java. Main.java đặt ở root src/ (không có package declaration để match project structure).</t>
+  </si>
+  <si>
+    <t>Algorithms – CSV Header Handling</t>
+  </si>
+  <si>
+    <t>loadAll() đọc dòng header của CSV vào như data, gây parse error vì 'empId' không thể parse thành int.</t>
+  </si>
+  <si>
+    <t>CsvRepository.loadAll() parse dòng đầu tiên (header) như data record, gây IllegalArgumentException. Cách fix mà không hardcode header string?</t>
+  </si>
+  <si>
+    <t>AI gợi ý: skip dòng i==0, hoặc check if first field matches header name, hoặc dùng abstract getHeader() method và compare.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Skip index 0 là đơn giản nhất. Check by header name phức tạp hơn không cần thiết. Tuy nhiên AI bỏ qua edge case: file mới tạo chỉ có header, loadAll() phải return empty list chứ không phải error.
+Contextualization: saveAll() luôn ghi header đầu tiên (qua getHeader()). Vậy file luôn có header ở line 1 khi được tạo bởi hệ thống.
+Creative Synthesis: `for (int i = 1; i &lt; lines.size(); i++)` – skip index 0. Bọc parse lỗi với CsvParseException ghi rõ line number và content để debug.
+Decision Ownership: Implement skip-header pattern ở CsvRepository.loadAll(). Subclass không cần lo về header khi gọi loadAll().</t>
+  </si>
+  <si>
+    <t>Pattern Recognition – CSV Parse Safety</t>
+  </si>
+  <si>
+    <t>Một số CSV field có thể rỗng (approvedBy khi LeaveRequest PENDING), split(",") bỏ trailing empty fields gây ArrayIndexOutOfBoundsException.</t>
+  </si>
+  <si>
+    <t>Java String.split(',') bỏ trailing empty strings. Khi CSV dòng có `...,PENDING,,2024-01-15` (approvedBy rỗng), split cho 9 phần tử thay vì 10. Fix thế nào?</t>
+  </si>
+  <si>
+    <t>AI giải thích: dùng split(',', -1) với limit=-1 giữ trailing empty strings. Limit=0 (default) bỏ trailing empties.</t>
+  </si>
+  <si>
+    <t>Algorithms – Performance Testing</t>
+  </si>
+  <si>
+    <t>Cần viết performance test cho AttendanceRepository với 12,000 records – threshold nên đặt bao nhiêu ms là hợp lý?</t>
+  </si>
+  <si>
+    <t>Performance test đọc 12,000 dòng CSV của AttendanceRepository nên đặt threshold bao nhiêu milliseconds để test meaningful nhưng không flaky?</t>
+  </si>
+  <si>
+    <t>AI gợi ý threshold 500ms là reasonable cho 12K records đọc từ disk. Nếu chạy trên CI/CD có thể nới lỏng lên 2000ms.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: AI gợi ý 500ms nhưng không tính đến JVM warm-up time. Lần đầu chạy test có thể chậm hơn do class loading và JIT.
+Contextualization: Test chạy trên local machine với SSD, không phải CI/CD. 12K records x 8 columns = nhỏ, dưới 1s là realistic.
+Creative Synthesis: Đặt threshold 1000ms (1 giây) thay vì 500ms để tránh flaky test trên hardware khác nhau. In execution time ra console để monitor.
+Decision Ownership: `assertTrue(timeMs &lt; 1000)` trong AttendancePerformanceTest. Đủ strict để phát hiện regression nhưng không quá strict.</t>
+  </si>
+  <si>
+    <t>Abstraction – Exception Hierarchy</t>
+  </si>
+  <si>
+    <t>Cần thiết kế exception hierarchy cho project: bao nhiêu custom exception, checked vs unchecked?</t>
+  </si>
+  <si>
+    <t>Project Payroll cần những custom exception nào? InsufficientLeaveException nên là checked hay unchecked? DuplicatePaymentException thì sao?</t>
+  </si>
+  <si>
+    <t>AI gợi ý: InsufficientLeaveException = checked (business rule violation, caller phải handle), DuplicatePaymentException và OptimisticLockException = unchecked (programming error).</t>
+  </si>
+  <si>
+    <t>Critical Thinking: AI đúng về phân loại. InsufficientLeaveException checked vì HR cần handle gracefully (show message, not crash). DuplicatePayment unchecked vì không nên xảy ra nếu code đúng.
+Contextualization: CsvParseException unchecked vì nếu CSV corrupt là system error, không phải business logic error. Caller không thể recover.
+Creative Synthesis: 4 exceptions: InsufficientLeaveException(checked), OptimisticLockException(unchecked), CsvParseException(unchecked với lineNumber field), DuplicatePaymentException(unchecked).
+Decision Ownership: Exception package riêng, mỗi exception có constructor nhận message. CsvParseException thêm lineContent và lineNumber để debug CSV errors.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: AI đúng hoàn toàn. split(',', -1) là fix chuẩn cho CSV với optional fields.
+Contextualization: LeaveRequest.approvedBy = '' khi PENDING,                        PayrollEntry.processedAt = '' khi PENDING – cả hai dùng split(',', -1) trong fromCsvLine().
+Creative Synthesis: Áp dụng split(',', -1) cho tất cả fromCsvLine() trong project. Thêm null-safe check: `approvedBy = parts[8].trim()` (không throw nếu rỗng).
+Decision Ownership: Standard pattern cho toàn project: tất cả fromCsvLine() dùng split(',', -1) và trim() từng field.</t>
+  </si>
+  <si>
+    <t>#011</t>
+  </si>
+  <si>
+    <t>#012</t>
+  </si>
+  <si>
+    <t>#013</t>
+  </si>
+  <si>
+    <t>#014</t>
+  </si>
+  <si>
+    <t>The issue "1.0E7" indicated that the salary value was stored incorrectly.</t>
+  </si>
+  <si>
+    <t>The salary value was correct. The problem was only the default scientific notation when printing a double in Employee.toString().</t>
+  </si>
+  <si>
+    <t>Checked Employee.java and confirmed that the value was stored correctly but displayed using Java's default formatting.</t>
+  </si>
+  <si>
+    <t>Changed Employee.toString() to use String.format("%,.0f", baseSalary) for readable salary output.</t>
+  </si>
+  <si>
+    <t>AttendanceRepository supports loadAll() inherited from CsvRepository.</t>
+  </si>
+  <si>
+    <t>The actual AttendanceRepository in the project did not implement loadAll(). It used a different API, so the suggested performance test could not compile.</t>
+  </si>
+  <si>
+    <t>Reviewed AttendanceRepository.java and compared it with the generated benchmark code.</t>
+  </si>
+  <si>
+    <t>Modified the performance test to use the actual repository method instead of loadAll().</t>
+  </si>
+  <si>
+    <t>The AI suggested using DecimalFormat to display numbers with comma separators and using Math.ceil(value / 1000.0) * 1000 to round salary values up to the nearest thousand.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: AI đúng.                                                                         Contextualization: Tôi đang dùng Repository cũ.                                                       Creative Synthesis: Chuyển EmployeeRepository sang Generic Repository.               Decision: Refactor thay vì thêm từng hàm riêng.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: AI đúng.                                                                         Contextualization: Test tạo Employee thiếu EmpType.                                               Creative Synthesis: Khởi tạo đầy đủ Employee trước khi add().                               Decision: Validate dữ liệu trước khi lưu.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Object linh hoạt hơn khi mở rộng.                                    Contextualization: Project có thể có nhiều SalaryCalculator.                                      Creative Synthesis: Chuyển sang instance methods.                                               Decision: Không dùng static.</t>
   </si>
 </sst>
 </file>
@@ -620,7 +744,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -705,12 +829,15 @@
       <charset val="163"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial Unicode MS"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -735,8 +862,18 @@
         <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F5F5"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -759,11 +896,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -821,8 +984,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1140,7 +1321,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
@@ -1149,59 +1330,59 @@
     <col min="5" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-    </row>
-    <row r="3" spans="1:6" ht="17.399999999999999">
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+    </row>
+    <row r="3" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="17.399999999999999">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
@@ -1209,7 +1390,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
@@ -1217,7 +1398,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
@@ -1229,7 +1410,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>13</v>
       </c>
@@ -1237,12 +1418,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="17.399999999999999">
+    <row r="15" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>16</v>
       </c>
@@ -1256,39 +1437,39 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>20</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>23</v>
       </c>
       <c r="D17" s="7"/>
     </row>
-    <row r="18" spans="1:4" ht="27.6">
+    <row r="18" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>22</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D18" s="7"/>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>24</v>
       </c>
@@ -1296,12 +1477,12 @@
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
     </row>
-    <row r="22" spans="1:4" ht="17.399999999999999">
+    <row r="22" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>26</v>
       </c>
@@ -1312,7 +1493,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>29</v>
       </c>
@@ -1323,7 +1504,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>31</v>
       </c>
@@ -1334,7 +1515,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>32</v>
       </c>
@@ -1345,7 +1526,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>33</v>
       </c>
@@ -1367,7 +1548,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.796875" customWidth="1"/>
     <col min="2" max="2" width="27.19921875" customWidth="1"/>
@@ -1375,35 +1556,21 @@
     <col min="4" max="4" width="32.09765625" customWidth="1"/>
     <col min="5" max="5" width="35.296875" customWidth="1"/>
     <col min="6" max="6" width="48.3984375" customWidth="1"/>
-    <col min="7" max="7" width="71.3984375" customWidth="1"/>
+    <col min="7" max="7" width="77.796875" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-    </row>
-    <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="25" t="s">
+    </row>
+    <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-    </row>
-    <row r="3" spans="1:8" ht="40.049999999999997" customHeight="1">
+    </row>
+    <row r="3" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>36</v>
       </c>
@@ -1429,280 +1596,372 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="167.4" customHeight="1">
-      <c r="A4" s="7">
-        <v>1</v>
+    <row r="4" spans="1:8" ht="103.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>117</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="H4" s="7"/>
+    </row>
+    <row r="5" spans="1:8" ht="137.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="H5" s="7"/>
+    </row>
+    <row r="6" spans="1:8" ht="87.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="H6" s="7"/>
+    </row>
+    <row r="7" spans="1:8" ht="138" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="83.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>158</v>
+      </c>
+      <c r="G8" s="26" t="s">
+        <v>219</v>
+      </c>
+      <c r="H8" s="7"/>
+    </row>
+    <row r="9" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>220</v>
+      </c>
+      <c r="H9" s="7"/>
+    </row>
+    <row r="10" spans="1:8" ht="93.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="B10" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E4" s="7" t="s">
+      <c r="C10" s="25" t="s">
+        <v>163</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>164</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="H10" s="7"/>
+    </row>
+    <row r="11" spans="1:8" ht="149.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="B11" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="137.4" customHeight="1">
-      <c r="A5" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="129" customHeight="1">
-      <c r="A6" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="100.2" customHeight="1">
-      <c r="A7" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="117.6" customHeight="1">
-      <c r="A8" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="H8" s="7"/>
-    </row>
-    <row r="9" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A9" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="H9" s="7"/>
-    </row>
-    <row r="10" spans="1:8" ht="143.4" customHeight="1">
-      <c r="A10" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="E10" s="7" t="s">
+      <c r="C11" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>188</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="G11" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="H11" s="7"/>
+    </row>
+    <row r="12" spans="1:8" ht="127.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="F10" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-    </row>
-    <row r="12" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
+      <c r="D12" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>173</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="G12" s="25" t="s">
+        <v>175</v>
+      </c>
       <c r="H12" s="7"/>
     </row>
-    <row r="13" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
+    <row r="13" spans="1:8" ht="139.19999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>198</v>
+      </c>
+      <c r="G13" s="25" t="s">
+        <v>199</v>
+      </c>
       <c r="H13" s="7"/>
     </row>
-    <row r="14" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
+    <row r="14" spans="1:8" ht="171.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="E14" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="F14" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="G14" s="25" t="s">
+        <v>180</v>
+      </c>
       <c r="H14" s="7"/>
     </row>
-    <row r="15" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
+    <row r="15" spans="1:8" ht="144" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>192</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="F15" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="G15" s="25" t="s">
+        <v>205</v>
+      </c>
       <c r="H15" s="7"/>
     </row>
-    <row r="16" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
+    <row r="16" spans="1:8" ht="163.19999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>181</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="F16" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="G16" s="25" t="s">
+        <v>185</v>
+      </c>
       <c r="H16" s="7"/>
     </row>
-    <row r="17" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
+    <row r="17" spans="1:8" ht="187.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>201</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="F17" s="25" t="s">
+        <v>203</v>
+      </c>
+      <c r="G17" s="25" t="s">
+        <v>204</v>
+      </c>
       <c r="H17" s="7"/>
     </row>
-    <row r="18" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
+    <row r="18" spans="1:8" ht="131.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="29"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
       <c r="H18" s="7"/>
     </row>
-    <row r="19" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
+    <row r="19" spans="1:8" ht="151.80000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="19"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
       <c r="H19" s="7"/>
     </row>
-    <row r="20" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
+    <row r="20" spans="1:8" ht="160.19999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="19"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="1:8" ht="79.95" customHeight="1">
+    <row r="21" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -1712,7 +1971,7 @@
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
     </row>
-    <row r="22" spans="1:8" ht="79.95" customHeight="1">
+    <row r="22" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -1722,7 +1981,7 @@
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
     </row>
-    <row r="23" spans="1:8" ht="79.95" customHeight="1">
+    <row r="23" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -1732,7 +1991,7 @@
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
     </row>
-    <row r="24" spans="1:8" ht="79.95" customHeight="1">
+    <row r="24" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -1742,7 +2001,7 @@
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
     </row>
-    <row r="25" spans="1:8" ht="79.95" customHeight="1">
+    <row r="25" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -1752,7 +2011,7 @@
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
     </row>
-    <row r="26" spans="1:8" ht="79.95" customHeight="1">
+    <row r="26" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -1763,10 +2022,6 @@
       <c r="H26" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1775,148 +2030,166 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F36"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="6" width="30" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
+    <col min="4" max="4" width="35.296875" customWidth="1"/>
+    <col min="5" max="5" width="41.59765625" customWidth="1"/>
+    <col min="6" max="6" width="32.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-    </row>
-    <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+    </row>
+    <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="F3" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="61.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="115.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="86.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>212</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="112.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="B8" s="27" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="60" customHeight="1">
-      <c r="A4" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-    </row>
-    <row r="6" spans="1:6" ht="60" customHeight="1">
-      <c r="A6" s="23" t="s">
-        <v>139</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="60" customHeight="1">
-      <c r="A7" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>163</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="60" customHeight="1">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-    </row>
-    <row r="9" spans="1:6" ht="60" customHeight="1">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-    </row>
-    <row r="10" spans="1:6" ht="60" customHeight="1">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-    </row>
-    <row r="11" spans="1:6" ht="60" customHeight="1">
+      <c r="C8" s="27" t="s">
+        <v>214</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>215</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>216</v>
+      </c>
+      <c r="F8" s="27" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="97.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="28"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+    </row>
+    <row r="10" spans="1:6" ht="109.8" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -1924,7 +2197,7 @@
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
     </row>
-    <row r="12" spans="1:6" ht="60" customHeight="1">
+    <row r="12" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -1932,7 +2205,7 @@
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
     </row>
-    <row r="13" spans="1:6" ht="60" customHeight="1">
+    <row r="13" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -1940,7 +2213,7 @@
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
     </row>
-    <row r="14" spans="1:6" ht="60" customHeight="1">
+    <row r="14" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -1948,7 +2221,7 @@
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
     </row>
-    <row r="15" spans="1:6" ht="60" customHeight="1">
+    <row r="15" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -1956,7 +2229,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
     </row>
-    <row r="16" spans="1:6" ht="60" customHeight="1">
+    <row r="16" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -1964,7 +2237,7 @@
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
     </row>
-    <row r="17" spans="1:6" ht="60" customHeight="1">
+    <row r="17" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -1972,7 +2245,7 @@
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
     </row>
-    <row r="18" spans="1:6" ht="60" customHeight="1">
+    <row r="18" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -1980,7 +2253,7 @@
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
     </row>
-    <row r="19" spans="1:6" ht="60" customHeight="1">
+    <row r="19" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -1988,7 +2261,7 @@
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
     </row>
-    <row r="20" spans="1:6" ht="60" customHeight="1">
+    <row r="20" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -1996,7 +2269,7 @@
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
     </row>
-    <row r="21" spans="1:6" ht="60" customHeight="1">
+    <row r="21" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -2004,7 +2277,7 @@
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
     </row>
-    <row r="22" spans="1:6" ht="60" customHeight="1">
+    <row r="22" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -2012,7 +2285,7 @@
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
     </row>
-    <row r="23" spans="1:6" ht="60" customHeight="1">
+    <row r="23" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -2020,7 +2293,7 @@
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
     </row>
-    <row r="24" spans="1:6" ht="60" customHeight="1">
+    <row r="24" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -2028,75 +2301,75 @@
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
     </row>
-    <row r="30" spans="1:6" ht="17.399999999999999">
+    <row r="30" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="27.6">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A34" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A36" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B36" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B32" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="27.6">
-      <c r="A33" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="27.6">
-      <c r="A34" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="27.6">
-      <c r="A35" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="41.4">
-      <c r="A36" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>95</v>
-      </c>
       <c r="C36" s="7" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -2111,7 +2384,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D30"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
@@ -2119,220 +2392,220 @@
     <col min="4" max="4" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="36" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+    </row>
+    <row r="4" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D6" s="13"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D7" s="13"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8" s="13"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" s="13"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D10" s="13"/>
+    </row>
+    <row r="12" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" s="13"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="30" t="s">
+      <c r="C15" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" s="13"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-    </row>
-    <row r="4" spans="1:4" ht="17.399999999999999">
-      <c r="A4" s="1" t="s">
+      <c r="C16" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="13"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" s="13" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="6" t="s">
+      <c r="C17" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D17" s="13"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="C18" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D18" s="13"/>
+    </row>
+    <row r="20" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="C5" s="6" t="s">
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="D5" s="11" t="s">
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="15" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="12" t="s">
+    <row r="25" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B6" s="13" t="s">
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D6" s="13"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D7" s="13"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D8" s="13"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D9" s="13"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D10" s="13"/>
-    </row>
-    <row r="12" spans="1:4" ht="17.399999999999999">
-      <c r="A12" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D14" s="13"/>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D15" s="13"/>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D16" s="13"/>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D17" s="13"/>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D18" s="13"/>
-    </row>
-    <row r="20" spans="1:4" ht="15.6">
-      <c r="A20" s="14" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="15" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="15" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="17.399999999999999">
-      <c r="A25" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="16" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="55.2">
+    </row>
+    <row r="27" spans="1:4" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
         <v>36</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>44</v>
       </c>
@@ -2340,17 +2613,17 @@
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
